--- a/Quarterly/Summary data/CERP_PBC_Summary_Data.xlsx
+++ b/Quarterly/Summary data/CERP_PBC_Summary_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erica.Williams\Documents\GitHub\Oyster-Reports\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erica.Levine\Documents\GitHub\Oyster-Reports\Quarterly\Summary data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D8DB0C3-B103-410B-93BD-9ED0CCCD6A2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A133C9-850A-40FF-9E53-8AFAA5264B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27630" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dermo Station" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,20 @@
     <sheet name="SH Station" sheetId="11" r:id="rId12"/>
     <sheet name="SH Site" sheetId="13" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2014,9 +2027,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CG40"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -2273,7 +2286,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>45017</v>
       </c>
@@ -2528,7 +2541,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>45047</v>
       </c>
@@ -2785,7 +2798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>45078</v>
       </c>
@@ -3042,7 +3055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>45108</v>
       </c>
@@ -3299,7 +3312,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>45139</v>
       </c>
@@ -3556,7 +3569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>45170</v>
       </c>
@@ -3813,7 +3826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>45200</v>
       </c>
@@ -4070,7 +4083,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>45231</v>
       </c>
@@ -4327,7 +4340,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>45261</v>
       </c>
@@ -4584,7 +4597,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>45292</v>
       </c>
@@ -4841,7 +4854,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>45323</v>
       </c>
@@ -5098,7 +5111,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>45352</v>
       </c>
@@ -5355,7 +5368,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>45383</v>
       </c>
@@ -5612,7 +5625,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>45413</v>
       </c>
@@ -5869,7 +5882,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>45444</v>
       </c>
@@ -6126,7 +6139,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>45474</v>
       </c>
@@ -6383,7 +6396,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>45505</v>
       </c>
@@ -6640,7 +6653,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>45536</v>
       </c>
@@ -6897,7 +6910,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>45566</v>
       </c>
@@ -7154,7 +7167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>45597</v>
       </c>
@@ -7402,7 +7415,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>45627</v>
       </c>
@@ -7650,7 +7663,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>45658</v>
       </c>
@@ -7898,7 +7911,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>45689</v>
       </c>
@@ -8146,7 +8159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>45717</v>
       </c>
@@ -8394,7 +8407,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>45748</v>
       </c>
@@ -8642,7 +8655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>45778</v>
       </c>
@@ -8890,7 +8903,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>45809</v>
       </c>
@@ -9138,7 +9151,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>45839</v>
       </c>
@@ -9395,7 +9408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>45870</v>
       </c>
@@ -9652,7 +9665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>45901</v>
       </c>
@@ -9909,7 +9922,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>45931</v>
       </c>
@@ -10166,7 +10179,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>45962</v>
       </c>
@@ -10423,7 +10436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>45992</v>
       </c>
@@ -10680,7 +10693,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>46023</v>
       </c>
@@ -10937,7 +10950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>46054</v>
       </c>
@@ -11194,7 +11207,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>46082</v>
       </c>
@@ -11451,7 +11464,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>46113</v>
       </c>
@@ -11708,7 +11721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>46143</v>
       </c>
@@ -11965,7 +11978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:85" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>46174</v>
       </c>
@@ -12231,113 +12244,113 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:CX14"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" customWidth="1"/>
-    <col min="4" max="4" width="13.33203125" customWidth="1"/>
-    <col min="5" max="5" width="20.88671875" customWidth="1"/>
-    <col min="6" max="6" width="18.88671875" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" customWidth="1"/>
-    <col min="8" max="8" width="13.33203125" customWidth="1"/>
-    <col min="9" max="9" width="20.88671875" customWidth="1"/>
-    <col min="10" max="10" width="18.88671875" customWidth="1"/>
-    <col min="11" max="11" width="15.88671875" customWidth="1"/>
-    <col min="12" max="12" width="13.88671875" customWidth="1"/>
-    <col min="13" max="13" width="21.5546875" customWidth="1"/>
-    <col min="14" max="14" width="19.44140625" customWidth="1"/>
-    <col min="15" max="15" width="15.88671875" customWidth="1"/>
-    <col min="16" max="16" width="13.88671875" customWidth="1"/>
-    <col min="17" max="17" width="21.5546875" customWidth="1"/>
-    <col min="18" max="18" width="19.44140625" customWidth="1"/>
-    <col min="19" max="19" width="15.33203125" customWidth="1"/>
-    <col min="20" max="20" width="13.33203125" customWidth="1"/>
-    <col min="21" max="21" width="20.88671875" customWidth="1"/>
-    <col min="22" max="22" width="18.6640625" customWidth="1"/>
-    <col min="23" max="23" width="15.33203125" customWidth="1"/>
-    <col min="24" max="24" width="12.5546875" customWidth="1"/>
-    <col min="25" max="25" width="21.44140625" customWidth="1"/>
-    <col min="26" max="26" width="18.6640625" customWidth="1"/>
-    <col min="27" max="27" width="15.33203125" customWidth="1"/>
-    <col min="28" max="28" width="12.5546875" customWidth="1"/>
-    <col min="29" max="29" width="21.44140625" customWidth="1"/>
-    <col min="30" max="30" width="18.6640625" customWidth="1"/>
-    <col min="31" max="31" width="15.5546875" customWidth="1"/>
-    <col min="32" max="32" width="12.88671875" customWidth="1"/>
-    <col min="33" max="33" width="21.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" customWidth="1"/>
+    <col min="9" max="9" width="20.85546875" customWidth="1"/>
+    <col min="10" max="10" width="18.85546875" customWidth="1"/>
+    <col min="11" max="11" width="15.85546875" customWidth="1"/>
+    <col min="12" max="12" width="13.85546875" customWidth="1"/>
+    <col min="13" max="13" width="21.5703125" customWidth="1"/>
+    <col min="14" max="14" width="19.42578125" customWidth="1"/>
+    <col min="15" max="15" width="15.85546875" customWidth="1"/>
+    <col min="16" max="16" width="13.85546875" customWidth="1"/>
+    <col min="17" max="17" width="21.5703125" customWidth="1"/>
+    <col min="18" max="18" width="19.42578125" customWidth="1"/>
+    <col min="19" max="19" width="15.28515625" customWidth="1"/>
+    <col min="20" max="20" width="13.28515625" customWidth="1"/>
+    <col min="21" max="21" width="20.85546875" customWidth="1"/>
+    <col min="22" max="22" width="18.7109375" customWidth="1"/>
+    <col min="23" max="23" width="15.28515625" customWidth="1"/>
+    <col min="24" max="24" width="12.5703125" customWidth="1"/>
+    <col min="25" max="25" width="21.42578125" customWidth="1"/>
+    <col min="26" max="26" width="18.7109375" customWidth="1"/>
+    <col min="27" max="27" width="15.28515625" customWidth="1"/>
+    <col min="28" max="28" width="12.5703125" customWidth="1"/>
+    <col min="29" max="29" width="21.42578125" customWidth="1"/>
+    <col min="30" max="30" width="18.7109375" customWidth="1"/>
+    <col min="31" max="31" width="15.5703125" customWidth="1"/>
+    <col min="32" max="32" width="12.85546875" customWidth="1"/>
+    <col min="33" max="33" width="21.7109375" customWidth="1"/>
     <col min="34" max="34" width="19" customWidth="1"/>
-    <col min="35" max="35" width="15.5546875" customWidth="1"/>
-    <col min="36" max="36" width="12.88671875" customWidth="1"/>
-    <col min="37" max="37" width="21.6640625" customWidth="1"/>
+    <col min="35" max="35" width="15.5703125" customWidth="1"/>
+    <col min="36" max="36" width="12.85546875" customWidth="1"/>
+    <col min="37" max="37" width="21.7109375" customWidth="1"/>
     <col min="38" max="38" width="19" customWidth="1"/>
-    <col min="39" max="39" width="15.5546875" customWidth="1"/>
-    <col min="40" max="40" width="12.88671875" customWidth="1"/>
-    <col min="41" max="41" width="21.6640625" customWidth="1"/>
+    <col min="39" max="39" width="15.5703125" customWidth="1"/>
+    <col min="40" max="40" width="12.85546875" customWidth="1"/>
+    <col min="41" max="41" width="21.7109375" customWidth="1"/>
     <col min="42" max="42" width="19" customWidth="1"/>
-    <col min="43" max="43" width="15.33203125" customWidth="1"/>
-    <col min="44" max="44" width="12.5546875" customWidth="1"/>
-    <col min="45" max="45" width="21.44140625" customWidth="1"/>
-    <col min="46" max="46" width="18.6640625" customWidth="1"/>
-    <col min="47" max="47" width="15.33203125" customWidth="1"/>
-    <col min="48" max="48" width="12.5546875" customWidth="1"/>
-    <col min="49" max="49" width="21.44140625" customWidth="1"/>
-    <col min="50" max="50" width="18.6640625" customWidth="1"/>
-    <col min="51" max="51" width="15.33203125" customWidth="1"/>
-    <col min="52" max="52" width="12.5546875" customWidth="1"/>
-    <col min="53" max="53" width="21.44140625" customWidth="1"/>
-    <col min="54" max="54" width="18.6640625" customWidth="1"/>
-    <col min="55" max="55" width="14.88671875" customWidth="1"/>
-    <col min="56" max="56" width="12.109375" customWidth="1"/>
-    <col min="57" max="57" width="20.88671875" customWidth="1"/>
-    <col min="58" max="58" width="18.33203125" customWidth="1"/>
-    <col min="59" max="59" width="14.88671875" customWidth="1"/>
-    <col min="60" max="60" width="12.109375" customWidth="1"/>
-    <col min="61" max="61" width="20.88671875" customWidth="1"/>
-    <col min="62" max="62" width="18.33203125" customWidth="1"/>
-    <col min="63" max="63" width="14.88671875" customWidth="1"/>
-    <col min="64" max="64" width="12.109375" customWidth="1"/>
-    <col min="65" max="65" width="20.88671875" customWidth="1"/>
-    <col min="66" max="66" width="18.33203125" customWidth="1"/>
-    <col min="67" max="67" width="14.88671875" customWidth="1"/>
-    <col min="68" max="68" width="12.109375" customWidth="1"/>
-    <col min="69" max="69" width="20.88671875" customWidth="1"/>
-    <col min="70" max="70" width="18.33203125" customWidth="1"/>
-    <col min="71" max="71" width="14.88671875" customWidth="1"/>
-    <col min="72" max="72" width="12.109375" customWidth="1"/>
-    <col min="73" max="73" width="20.88671875" customWidth="1"/>
-    <col min="74" max="74" width="18.33203125" customWidth="1"/>
-    <col min="75" max="75" width="14.88671875" customWidth="1"/>
-    <col min="76" max="76" width="12.109375" customWidth="1"/>
-    <col min="77" max="77" width="20.88671875" customWidth="1"/>
-    <col min="78" max="78" width="18.33203125" customWidth="1"/>
-    <col min="79" max="79" width="15.109375" customWidth="1"/>
-    <col min="80" max="80" width="12.44140625" customWidth="1"/>
-    <col min="81" max="81" width="21.109375" customWidth="1"/>
-    <col min="82" max="82" width="18.5546875" customWidth="1"/>
-    <col min="83" max="83" width="15.109375" customWidth="1"/>
-    <col min="84" max="84" width="12.44140625" customWidth="1"/>
-    <col min="85" max="85" width="21.109375" customWidth="1"/>
-    <col min="86" max="86" width="18.5546875" customWidth="1"/>
-    <col min="87" max="87" width="15.109375" customWidth="1"/>
-    <col min="88" max="88" width="12.44140625" customWidth="1"/>
-    <col min="89" max="89" width="21.109375" customWidth="1"/>
-    <col min="90" max="90" width="18.5546875" customWidth="1"/>
-    <col min="91" max="91" width="14.6640625" customWidth="1"/>
+    <col min="43" max="43" width="15.28515625" customWidth="1"/>
+    <col min="44" max="44" width="12.5703125" customWidth="1"/>
+    <col min="45" max="45" width="21.42578125" customWidth="1"/>
+    <col min="46" max="46" width="18.7109375" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="12.5703125" customWidth="1"/>
+    <col min="49" max="49" width="21.42578125" customWidth="1"/>
+    <col min="50" max="50" width="18.7109375" customWidth="1"/>
+    <col min="51" max="51" width="15.28515625" customWidth="1"/>
+    <col min="52" max="52" width="12.5703125" customWidth="1"/>
+    <col min="53" max="53" width="21.42578125" customWidth="1"/>
+    <col min="54" max="54" width="18.7109375" customWidth="1"/>
+    <col min="55" max="55" width="14.85546875" customWidth="1"/>
+    <col min="56" max="56" width="12.140625" customWidth="1"/>
+    <col min="57" max="57" width="20.85546875" customWidth="1"/>
+    <col min="58" max="58" width="18.28515625" customWidth="1"/>
+    <col min="59" max="59" width="14.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.140625" customWidth="1"/>
+    <col min="61" max="61" width="20.85546875" customWidth="1"/>
+    <col min="62" max="62" width="18.28515625" customWidth="1"/>
+    <col min="63" max="63" width="14.85546875" customWidth="1"/>
+    <col min="64" max="64" width="12.140625" customWidth="1"/>
+    <col min="65" max="65" width="20.85546875" customWidth="1"/>
+    <col min="66" max="66" width="18.28515625" customWidth="1"/>
+    <col min="67" max="67" width="14.85546875" customWidth="1"/>
+    <col min="68" max="68" width="12.140625" customWidth="1"/>
+    <col min="69" max="69" width="20.85546875" customWidth="1"/>
+    <col min="70" max="70" width="18.28515625" customWidth="1"/>
+    <col min="71" max="71" width="14.85546875" customWidth="1"/>
+    <col min="72" max="72" width="12.140625" customWidth="1"/>
+    <col min="73" max="73" width="20.85546875" customWidth="1"/>
+    <col min="74" max="74" width="18.28515625" customWidth="1"/>
+    <col min="75" max="75" width="14.85546875" customWidth="1"/>
+    <col min="76" max="76" width="12.140625" customWidth="1"/>
+    <col min="77" max="77" width="20.85546875" customWidth="1"/>
+    <col min="78" max="78" width="18.28515625" customWidth="1"/>
+    <col min="79" max="79" width="15.140625" customWidth="1"/>
+    <col min="80" max="80" width="12.42578125" customWidth="1"/>
+    <col min="81" max="81" width="21.140625" customWidth="1"/>
+    <col min="82" max="82" width="18.5703125" customWidth="1"/>
+    <col min="83" max="83" width="15.140625" customWidth="1"/>
+    <col min="84" max="84" width="12.42578125" customWidth="1"/>
+    <col min="85" max="85" width="21.140625" customWidth="1"/>
+    <col min="86" max="86" width="18.5703125" customWidth="1"/>
+    <col min="87" max="87" width="15.140625" customWidth="1"/>
+    <col min="88" max="88" width="12.42578125" customWidth="1"/>
+    <col min="89" max="89" width="21.140625" customWidth="1"/>
+    <col min="90" max="90" width="18.5703125" customWidth="1"/>
+    <col min="91" max="91" width="14.7109375" customWidth="1"/>
     <col min="92" max="92" width="12" customWidth="1"/>
-    <col min="93" max="93" width="20.6640625" customWidth="1"/>
-    <col min="94" max="94" width="18.109375" customWidth="1"/>
-    <col min="95" max="95" width="14.6640625" customWidth="1"/>
+    <col min="93" max="93" width="20.7109375" customWidth="1"/>
+    <col min="94" max="94" width="18.140625" customWidth="1"/>
+    <col min="95" max="95" width="14.7109375" customWidth="1"/>
     <col min="96" max="96" width="12" customWidth="1"/>
-    <col min="97" max="97" width="20.6640625" customWidth="1"/>
-    <col min="98" max="98" width="18.109375" customWidth="1"/>
-    <col min="99" max="99" width="14.6640625" customWidth="1"/>
+    <col min="97" max="97" width="20.7109375" customWidth="1"/>
+    <col min="98" max="98" width="18.140625" customWidth="1"/>
+    <col min="99" max="99" width="14.7109375" customWidth="1"/>
     <col min="100" max="100" width="12" customWidth="1"/>
-    <col min="101" max="101" width="20.6640625" customWidth="1"/>
-    <col min="102" max="102" width="18.109375" customWidth="1"/>
+    <col min="101" max="101" width="20.7109375" customWidth="1"/>
+    <col min="102" max="102" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:102" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>286</v>
       </c>
@@ -12645,7 +12658,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="2" spans="1:102" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>386</v>
       </c>
@@ -12713,7 +12726,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="3" spans="1:102" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>387</v>
       </c>
@@ -13021,7 +13034,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="4" spans="1:102" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>388</v>
       </c>
@@ -13089,7 +13102,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="5" spans="1:102" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>389</v>
       </c>
@@ -13397,7 +13410,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="6" spans="1:102" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>390</v>
       </c>
@@ -13465,7 +13478,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="7" spans="1:102" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>391</v>
       </c>
@@ -13773,7 +13786,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="8" spans="1:102" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>392</v>
       </c>
@@ -13841,7 +13854,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="9" spans="1:102" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>393</v>
       </c>
@@ -14149,7 +14162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:102" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>495</v>
       </c>
@@ -14205,7 +14218,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="11" spans="1:102" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>496</v>
       </c>
@@ -14513,7 +14526,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="12" spans="1:102" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>497</v>
       </c>
@@ -14557,7 +14570,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:102" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>498</v>
       </c>
@@ -14865,7 +14878,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="14" spans="1:102" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>499</v>
       </c>
@@ -14918,16 +14931,16 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:AL14"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" customWidth="1"/>
-    <col min="3" max="3" width="9.5546875" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" customWidth="1"/>
-    <col min="5" max="5" width="15.109375" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>286</v>
       </c>
@@ -15043,7 +15056,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>386</v>
       </c>
@@ -15087,7 +15100,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>387</v>
       </c>
@@ -15203,7 +15216,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>388</v>
       </c>
@@ -15247,7 +15260,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>389</v>
       </c>
@@ -15363,7 +15376,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>390</v>
       </c>
@@ -15407,7 +15420,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>391</v>
       </c>
@@ -15523,7 +15536,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>392</v>
       </c>
@@ -15567,7 +15580,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>393</v>
       </c>
@@ -15683,7 +15696,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>394</v>
       </c>
@@ -15727,7 +15740,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>496</v>
       </c>
@@ -15843,7 +15856,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>497</v>
       </c>
@@ -15887,7 +15900,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>498</v>
       </c>
@@ -16003,7 +16016,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>499</v>
       </c>
@@ -16056,10 +16069,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:AZ14"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.5546875" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.5703125" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
@@ -16071,7 +16084,7 @@
     <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>286</v>
       </c>
@@ -16229,7 +16242,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="2" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>386</v>
       </c>
@@ -16267,7 +16280,7 @@
         <v>15.95</v>
       </c>
     </row>
-    <row r="3" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>387</v>
       </c>
@@ -16425,7 +16438,7 @@
         <v>16.79</v>
       </c>
     </row>
-    <row r="4" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>388</v>
       </c>
@@ -16463,7 +16476,7 @@
         <v>14.72</v>
       </c>
     </row>
-    <row r="5" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>389</v>
       </c>
@@ -16621,7 +16634,7 @@
         <v>22.27</v>
       </c>
     </row>
-    <row r="6" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>390</v>
       </c>
@@ -16659,7 +16672,7 @@
         <v>15.79</v>
       </c>
     </row>
-    <row r="7" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>391</v>
       </c>
@@ -16817,7 +16830,7 @@
         <v>14.19</v>
       </c>
     </row>
-    <row r="8" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>392</v>
       </c>
@@ -16855,7 +16868,7 @@
         <v>15.75</v>
       </c>
     </row>
-    <row r="9" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>393</v>
       </c>
@@ -17007,7 +17020,7 @@
         <v>17.510000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>495</v>
       </c>
@@ -17033,7 +17046,7 @@
         <v>17.149999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>496</v>
       </c>
@@ -17191,7 +17204,7 @@
         <v>7.54</v>
       </c>
     </row>
-    <row r="12" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>497</v>
       </c>
@@ -17217,7 +17230,7 @@
         <v>23.02</v>
       </c>
     </row>
-    <row r="13" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>498</v>
       </c>
@@ -17375,7 +17388,7 @@
         <v>18.93</v>
       </c>
     </row>
-    <row r="14" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>499</v>
       </c>
@@ -17410,14 +17423,14 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:T14"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" customWidth="1"/>
     <col min="3" max="3" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>286</v>
       </c>
@@ -17479,7 +17492,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>386</v>
       </c>
@@ -17505,7 +17518,7 @@
         <v>15.95</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>387</v>
       </c>
@@ -17567,7 +17580,7 @@
         <v>23.57</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>388</v>
       </c>
@@ -17593,7 +17606,7 @@
         <v>14.72</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>389</v>
       </c>
@@ -17655,7 +17668,7 @@
         <v>23.59</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>390</v>
       </c>
@@ -17681,7 +17694,7 @@
         <v>15.79</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>391</v>
       </c>
@@ -17743,7 +17756,7 @@
         <v>18.79</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>392</v>
       </c>
@@ -17769,7 +17782,7 @@
         <v>15.75</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>393</v>
       </c>
@@ -17831,7 +17844,7 @@
         <v>19.04</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>394</v>
       </c>
@@ -17857,7 +17870,7 @@
         <v>17.149999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>496</v>
       </c>
@@ -17919,7 +17932,7 @@
         <v>14.96</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>497</v>
       </c>
@@ -17945,7 +17958,7 @@
         <v>23.02</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>498</v>
       </c>
@@ -18007,7 +18020,7 @@
         <v>19.96</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>499</v>
       </c>
@@ -18042,9 +18055,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BQ40"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:69" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:69" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>5</v>
       </c>
@@ -18189,7 +18202,7 @@
       <c r="BP1" s="10"/>
       <c r="BQ1" s="10"/>
     </row>
-    <row r="2" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>45017</v>
       </c>
@@ -18302,7 +18315,7 @@
         <v>26.67</v>
       </c>
     </row>
-    <row r="3" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>45047</v>
       </c>
@@ -18415,7 +18428,7 @@
         <v>33.33</v>
       </c>
     </row>
-    <row r="4" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>45078</v>
       </c>
@@ -18528,7 +18541,7 @@
         <v>46.67</v>
       </c>
     </row>
-    <row r="5" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>45108</v>
       </c>
@@ -18641,7 +18654,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>45139</v>
       </c>
@@ -18754,7 +18767,7 @@
         <v>33.33</v>
       </c>
     </row>
-    <row r="7" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>45170</v>
       </c>
@@ -18867,7 +18880,7 @@
         <v>26.67</v>
       </c>
     </row>
-    <row r="8" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>45200</v>
       </c>
@@ -18980,7 +18993,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>45231</v>
       </c>
@@ -19093,7 +19106,7 @@
         <v>53.33</v>
       </c>
     </row>
-    <row r="10" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>45261</v>
       </c>
@@ -19206,7 +19219,7 @@
         <v>13.33</v>
       </c>
     </row>
-    <row r="11" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>45292</v>
       </c>
@@ -19319,7 +19332,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>45323</v>
       </c>
@@ -19432,7 +19445,7 @@
         <v>46.67</v>
       </c>
     </row>
-    <row r="13" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>45352</v>
       </c>
@@ -19545,7 +19558,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>45383</v>
       </c>
@@ -19658,7 +19671,7 @@
         <v>13.33</v>
       </c>
     </row>
-    <row r="15" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>45413</v>
       </c>
@@ -19771,7 +19784,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>45444</v>
       </c>
@@ -19884,7 +19897,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>45474</v>
       </c>
@@ -19997,7 +20010,7 @@
         <v>33.33</v>
       </c>
     </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>45505</v>
       </c>
@@ -20110,7 +20123,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>45536</v>
       </c>
@@ -20223,7 +20236,7 @@
         <v>66.67</v>
       </c>
     </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>45566</v>
       </c>
@@ -20336,7 +20349,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>45597</v>
       </c>
@@ -20449,7 +20462,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>45627</v>
       </c>
@@ -20562,7 +20575,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>45658</v>
       </c>
@@ -20675,7 +20688,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>45689</v>
       </c>
@@ -20788,7 +20801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>45717</v>
       </c>
@@ -20901,7 +20914,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>45748</v>
       </c>
@@ -21014,7 +21027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>45778</v>
       </c>
@@ -21127,7 +21140,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>45809</v>
       </c>
@@ -21240,7 +21253,7 @@
         <v>33.33</v>
       </c>
     </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>45839</v>
       </c>
@@ -21353,7 +21366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>45870</v>
       </c>
@@ -21466,7 +21479,7 @@
         <v>13.33</v>
       </c>
     </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>45901</v>
       </c>
@@ -21579,7 +21592,7 @@
         <v>33.33</v>
       </c>
     </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>45931</v>
       </c>
@@ -21692,7 +21705,7 @@
         <v>33.33</v>
       </c>
     </row>
-    <row r="33" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>45962</v>
       </c>
@@ -21805,7 +21818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>45992</v>
       </c>
@@ -21918,7 +21931,7 @@
         <v>73.33</v>
       </c>
     </row>
-    <row r="35" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>46023</v>
       </c>
@@ -22031,7 +22044,7 @@
         <v>33.33</v>
       </c>
     </row>
-    <row r="36" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>46054</v>
       </c>
@@ -22144,7 +22157,7 @@
         <v>13.33</v>
       </c>
     </row>
-    <row r="37" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>46082</v>
       </c>
@@ -22257,7 +22270,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>46113</v>
       </c>
@@ -22370,7 +22383,7 @@
         <v>26.67</v>
       </c>
     </row>
-    <row r="39" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>46143</v>
       </c>
@@ -22483,7 +22496,7 @@
         <v>26.67</v>
       </c>
     </row>
-    <row r="40" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>46174</v>
       </c>
@@ -22605,61 +22618,61 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:BM40"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" customWidth="1"/>
-    <col min="3" max="3" width="19.44140625" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" customWidth="1"/>
-    <col min="5" max="5" width="18.6640625" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="20.109375" customWidth="1"/>
-    <col min="8" max="8" width="19.44140625" customWidth="1"/>
-    <col min="9" max="11" width="16.6640625" customWidth="1"/>
-    <col min="12" max="12" width="20.109375" customWidth="1"/>
-    <col min="13" max="13" width="19.33203125" customWidth="1"/>
-    <col min="14" max="16" width="16.5546875" customWidth="1"/>
+    <col min="7" max="7" width="20.140625" customWidth="1"/>
+    <col min="8" max="8" width="19.42578125" customWidth="1"/>
+    <col min="9" max="11" width="16.7109375" customWidth="1"/>
+    <col min="12" max="12" width="20.140625" customWidth="1"/>
+    <col min="13" max="13" width="19.28515625" customWidth="1"/>
+    <col min="14" max="16" width="16.5703125" customWidth="1"/>
     <col min="17" max="17" width="20" customWidth="1"/>
-    <col min="18" max="18" width="13.44140625" customWidth="1"/>
-    <col min="19" max="19" width="20.109375" customWidth="1"/>
-    <col min="20" max="20" width="17.5546875" customWidth="1"/>
-    <col min="21" max="21" width="19.44140625" customWidth="1"/>
-    <col min="22" max="22" width="16.6640625" customWidth="1"/>
-    <col min="23" max="23" width="20.88671875" customWidth="1"/>
-    <col min="24" max="24" width="20.109375" customWidth="1"/>
-    <col min="25" max="27" width="17.5546875" customWidth="1"/>
-    <col min="28" max="28" width="20.88671875" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" customWidth="1"/>
+    <col min="19" max="19" width="20.140625" customWidth="1"/>
+    <col min="20" max="20" width="17.5703125" customWidth="1"/>
+    <col min="21" max="21" width="19.42578125" customWidth="1"/>
+    <col min="22" max="22" width="16.7109375" customWidth="1"/>
+    <col min="23" max="23" width="20.85546875" customWidth="1"/>
+    <col min="24" max="24" width="20.140625" customWidth="1"/>
+    <col min="25" max="27" width="17.5703125" customWidth="1"/>
+    <col min="28" max="28" width="20.85546875" customWidth="1"/>
     <col min="29" max="29" width="20" customWidth="1"/>
-    <col min="30" max="32" width="17.44140625" customWidth="1"/>
-    <col min="33" max="33" width="20.6640625" customWidth="1"/>
-    <col min="34" max="34" width="12.6640625" customWidth="1"/>
-    <col min="35" max="35" width="19.5546875" customWidth="1"/>
-    <col min="36" max="36" width="16.88671875" customWidth="1"/>
-    <col min="37" max="37" width="18.88671875" customWidth="1"/>
-    <col min="38" max="38" width="16.109375" customWidth="1"/>
-    <col min="39" max="39" width="20.33203125" customWidth="1"/>
-    <col min="40" max="40" width="19.5546875" customWidth="1"/>
-    <col min="41" max="43" width="16.88671875" customWidth="1"/>
-    <col min="44" max="44" width="20.33203125" customWidth="1"/>
-    <col min="45" max="45" width="19.44140625" customWidth="1"/>
-    <col min="46" max="48" width="16.6640625" customWidth="1"/>
-    <col min="49" max="49" width="20.109375" customWidth="1"/>
-    <col min="50" max="50" width="12.33203125" customWidth="1"/>
-    <col min="51" max="51" width="19.109375" customWidth="1"/>
-    <col min="52" max="52" width="16.44140625" customWidth="1"/>
-    <col min="53" max="53" width="18.44140625" customWidth="1"/>
-    <col min="54" max="54" width="15.6640625" customWidth="1"/>
-    <col min="55" max="55" width="19.88671875" customWidth="1"/>
-    <col min="56" max="56" width="19.109375" customWidth="1"/>
-    <col min="57" max="59" width="16.44140625" customWidth="1"/>
-    <col min="60" max="60" width="19.88671875" customWidth="1"/>
+    <col min="30" max="32" width="17.42578125" customWidth="1"/>
+    <col min="33" max="33" width="20.7109375" customWidth="1"/>
+    <col min="34" max="34" width="12.7109375" customWidth="1"/>
+    <col min="35" max="35" width="19.5703125" customWidth="1"/>
+    <col min="36" max="36" width="16.85546875" customWidth="1"/>
+    <col min="37" max="37" width="18.85546875" customWidth="1"/>
+    <col min="38" max="38" width="16.140625" customWidth="1"/>
+    <col min="39" max="39" width="20.28515625" customWidth="1"/>
+    <col min="40" max="40" width="19.5703125" customWidth="1"/>
+    <col min="41" max="43" width="16.85546875" customWidth="1"/>
+    <col min="44" max="44" width="20.28515625" customWidth="1"/>
+    <col min="45" max="45" width="19.42578125" customWidth="1"/>
+    <col min="46" max="48" width="16.7109375" customWidth="1"/>
+    <col min="49" max="49" width="20.140625" customWidth="1"/>
+    <col min="50" max="50" width="12.28515625" customWidth="1"/>
+    <col min="51" max="51" width="19.140625" customWidth="1"/>
+    <col min="52" max="52" width="16.42578125" customWidth="1"/>
+    <col min="53" max="53" width="18.42578125" customWidth="1"/>
+    <col min="54" max="54" width="15.7109375" customWidth="1"/>
+    <col min="55" max="55" width="19.85546875" customWidth="1"/>
+    <col min="56" max="56" width="19.140625" customWidth="1"/>
+    <col min="57" max="59" width="16.42578125" customWidth="1"/>
+    <col min="60" max="60" width="19.85546875" customWidth="1"/>
     <col min="61" max="61" width="19" customWidth="1"/>
-    <col min="62" max="62" width="16.33203125" customWidth="1"/>
-    <col min="63" max="64" width="16.44140625" customWidth="1"/>
-    <col min="65" max="65" width="19.6640625" customWidth="1"/>
+    <col min="62" max="62" width="16.28515625" customWidth="1"/>
+    <col min="63" max="64" width="16.42578125" customWidth="1"/>
+    <col min="65" max="65" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>5</v>
       </c>
@@ -22856,7 +22869,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="2" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>45017</v>
       </c>
@@ -23045,7 +23058,7 @@
         <v>43.33</v>
       </c>
     </row>
-    <row r="3" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>45047</v>
       </c>
@@ -23226,7 +23239,7 @@
         <v>36.67</v>
       </c>
     </row>
-    <row r="4" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>45078</v>
       </c>
@@ -23423,7 +23436,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>45108</v>
       </c>
@@ -23614,7 +23627,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>45139</v>
       </c>
@@ -23807,7 +23820,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>45170</v>
       </c>
@@ -24000,7 +24013,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>45200</v>
       </c>
@@ -24193,7 +24206,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="9" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>45231</v>
       </c>
@@ -24382,7 +24395,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>45261</v>
       </c>
@@ -24567,7 +24580,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>45292</v>
       </c>
@@ -24746,7 +24759,7 @@
       <c r="BL11" s="13"/>
       <c r="BM11" s="13"/>
     </row>
-    <row r="12" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>45323</v>
       </c>
@@ -24935,7 +24948,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="13" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>45352</v>
       </c>
@@ -25128,7 +25141,7 @@
         <v>26.67</v>
       </c>
     </row>
-    <row r="14" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>45383</v>
       </c>
@@ -25315,7 +25328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>45413</v>
       </c>
@@ -25499,7 +25512,7 @@
         <v>53.33</v>
       </c>
     </row>
-    <row r="16" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>45444</v>
       </c>
@@ -25691,7 +25704,7 @@
         <v>16.670000000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>45474</v>
       </c>
@@ -25888,7 +25901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>45505</v>
       </c>
@@ -26079,7 +26092,7 @@
         <v>36.67</v>
       </c>
     </row>
-    <row r="19" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>45536</v>
       </c>
@@ -26276,7 +26289,7 @@
         <v>73.33</v>
       </c>
     </row>
-    <row r="20" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>45566</v>
       </c>
@@ -26461,7 +26474,7 @@
         <v>26.67</v>
       </c>
     </row>
-    <row r="21" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>45597</v>
       </c>
@@ -26652,7 +26665,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="22" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>45627</v>
       </c>
@@ -26843,7 +26856,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>45658</v>
       </c>
@@ -27040,7 +27053,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>45689</v>
       </c>
@@ -27237,7 +27250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>45717</v>
       </c>
@@ -27434,7 +27447,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="26" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>45748</v>
       </c>
@@ -27625,7 +27638,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>45778</v>
       </c>
@@ -27822,7 +27835,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="28" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>45809</v>
       </c>
@@ -28016,7 +28029,7 @@
         <v>26.67</v>
       </c>
     </row>
-    <row r="29" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>45839</v>
       </c>
@@ -28210,7 +28223,7 @@
         <v>86.67</v>
       </c>
     </row>
-    <row r="30" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>45870</v>
       </c>
@@ -28404,7 +28417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>45901</v>
       </c>
@@ -28598,7 +28611,7 @@
         <v>13.33</v>
       </c>
     </row>
-    <row r="32" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>45931</v>
       </c>
@@ -28786,7 +28799,7 @@
         <v>13.33</v>
       </c>
     </row>
-    <row r="33" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>45962</v>
       </c>
@@ -28977,7 +28990,7 @@
         <v>13.33</v>
       </c>
     </row>
-    <row r="34" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>45992</v>
       </c>
@@ -29171,7 +29184,7 @@
         <v>16.670000000000002</v>
       </c>
     </row>
-    <row r="35" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>46023</v>
       </c>
@@ -29368,7 +29381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>46054</v>
       </c>
@@ -29565,7 +29578,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="37" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>46082</v>
       </c>
@@ -29762,7 +29775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>46113</v>
       </c>
@@ -29956,7 +29969,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="39" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>46143</v>
       </c>
@@ -30150,7 +30163,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>46174</v>
       </c>
@@ -30353,36 +30366,36 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Y40"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" customWidth="1"/>
-    <col min="7" max="7" width="15.5546875" customWidth="1"/>
-    <col min="8" max="8" width="18.33203125" customWidth="1"/>
-    <col min="9" max="9" width="15.5546875" customWidth="1"/>
-    <col min="10" max="10" width="17.5546875" customWidth="1"/>
-    <col min="11" max="11" width="14.88671875" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" customWidth="1"/>
+    <col min="8" max="8" width="18.28515625" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
+    <col min="10" max="10" width="17.5703125" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" customWidth="1"/>
     <col min="12" max="12" width="19" customWidth="1"/>
-    <col min="13" max="13" width="16.33203125" customWidth="1"/>
-    <col min="14" max="14" width="17.6640625" customWidth="1"/>
+    <col min="13" max="13" width="16.28515625" customWidth="1"/>
+    <col min="14" max="14" width="17.7109375" customWidth="1"/>
     <col min="15" max="15" width="15" customWidth="1"/>
-    <col min="16" max="16" width="16.88671875" customWidth="1"/>
-    <col min="17" max="17" width="14.33203125" customWidth="1"/>
-    <col min="18" max="18" width="18.44140625" customWidth="1"/>
-    <col min="19" max="19" width="15.6640625" customWidth="1"/>
-    <col min="20" max="20" width="17.33203125" customWidth="1"/>
-    <col min="21" max="21" width="14.5546875" customWidth="1"/>
-    <col min="22" max="22" width="16.44140625" customWidth="1"/>
-    <col min="23" max="23" width="13.88671875" customWidth="1"/>
+    <col min="16" max="16" width="16.85546875" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" customWidth="1"/>
+    <col min="18" max="18" width="18.42578125" customWidth="1"/>
+    <col min="19" max="19" width="15.7109375" customWidth="1"/>
+    <col min="20" max="20" width="17.28515625" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" customWidth="1"/>
+    <col min="22" max="22" width="16.42578125" customWidth="1"/>
+    <col min="23" max="23" width="13.85546875" customWidth="1"/>
     <col min="24" max="24" width="18" customWidth="1"/>
-    <col min="25" max="25" width="15.33203125" customWidth="1"/>
+    <col min="25" max="25" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>5</v>
       </c>
@@ -30459,7 +30472,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
         <v>45017</v>
       </c>
@@ -30536,7 +30549,7 @@
         <v>44.01</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>45047</v>
       </c>
@@ -30613,7 +30626,7 @@
         <v>36.57</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <v>45078</v>
       </c>
@@ -30690,7 +30703,7 @@
         <v>16.78</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <v>45108</v>
       </c>
@@ -30767,7 +30780,7 @@
         <v>47.26</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>45139</v>
       </c>
@@ -30844,7 +30857,7 @@
         <v>37.17</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>45170</v>
       </c>
@@ -30921,7 +30934,7 @@
         <v>45.26</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>45200</v>
       </c>
@@ -30998,7 +31011,7 @@
         <v>53.16</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>45231</v>
       </c>
@@ -31075,7 +31088,7 @@
         <v>26.94</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>45261</v>
       </c>
@@ -31148,7 +31161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>45292</v>
       </c>
@@ -31221,7 +31234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>45323</v>
       </c>
@@ -31298,7 +31311,7 @@
         <v>55.81</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>45352</v>
       </c>
@@ -31375,7 +31388,7 @@
         <v>26.67</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>45383</v>
       </c>
@@ -31452,7 +31465,7 @@
         <v>1.92</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>45413</v>
       </c>
@@ -31529,7 +31542,7 @@
         <v>26.94</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>45444</v>
       </c>
@@ -31606,7 +31619,7 @@
         <v>44.76</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>45474</v>
       </c>
@@ -31683,7 +31696,7 @@
         <v>42.86</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>45505</v>
       </c>
@@ -31760,7 +31773,7 @@
         <v>36.67</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>45536</v>
       </c>
@@ -31837,7 +31850,7 @@
         <v>21.43</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>45566</v>
       </c>
@@ -31914,7 +31927,7 @@
         <v>8.39</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>45597</v>
       </c>
@@ -31991,7 +32004,7 @@
         <v>18.95</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>45627</v>
       </c>
@@ -32068,7 +32081,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>45658</v>
       </c>
@@ -32145,7 +32158,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>45689</v>
       </c>
@@ -32222,7 +32235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>45717</v>
       </c>
@@ -32299,7 +32312,7 @@
         <v>1.92</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>45748</v>
       </c>
@@ -32376,7 +32389,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>45778</v>
       </c>
@@ -32453,7 +32466,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>45809</v>
       </c>
@@ -32530,7 +32543,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>45839</v>
       </c>
@@ -32607,7 +32620,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>45870</v>
       </c>
@@ -32684,7 +32697,7 @@
         <v>13.88</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>45901</v>
       </c>
@@ -32761,7 +32774,7 @@
         <v>5.09</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>45931</v>
       </c>
@@ -32838,7 +32851,7 @@
         <v>54.3</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>45962</v>
       </c>
@@ -32915,7 +32928,7 @@
         <v>17.32</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>45992</v>
       </c>
@@ -32992,7 +33005,7 @@
         <v>8.39</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>46023</v>
       </c>
@@ -33069,7 +33082,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>46054</v>
       </c>
@@ -33146,7 +33159,7 @@
         <v>1.92</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>46082</v>
       </c>
@@ -33223,7 +33236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>46113</v>
       </c>
@@ -33300,7 +33313,7 @@
         <v>5.77</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>46143</v>
       </c>
@@ -33377,7 +33390,7 @@
         <v>5.09</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>46174</v>
       </c>
@@ -33463,66 +33476,66 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:BH40"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" customWidth="1"/>
-    <col min="8" max="8" width="12.44140625" customWidth="1"/>
-    <col min="9" max="9" width="9.88671875" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" customWidth="1"/>
-    <col min="11" max="11" width="9.88671875" customWidth="1"/>
-    <col min="12" max="12" width="12.6640625" customWidth="1"/>
-    <col min="13" max="13" width="11.88671875" customWidth="1"/>
-    <col min="14" max="14" width="9.33203125" customWidth="1"/>
-    <col min="15" max="15" width="11.88671875" customWidth="1"/>
-    <col min="16" max="16" width="9.33203125" customWidth="1"/>
-    <col min="17" max="17" width="11.88671875" customWidth="1"/>
-    <col min="18" max="18" width="9.33203125" customWidth="1"/>
-    <col min="19" max="19" width="13.109375" customWidth="1"/>
-    <col min="20" max="20" width="12.109375" customWidth="1"/>
-    <col min="21" max="21" width="9.5546875" customWidth="1"/>
-    <col min="22" max="22" width="12.109375" customWidth="1"/>
-    <col min="23" max="23" width="9.5546875" customWidth="1"/>
-    <col min="24" max="24" width="12.109375" customWidth="1"/>
-    <col min="25" max="25" width="9.5546875" customWidth="1"/>
-    <col min="26" max="26" width="12.6640625" customWidth="1"/>
-    <col min="27" max="27" width="11.88671875" customWidth="1"/>
-    <col min="28" max="28" width="9.33203125" customWidth="1"/>
-    <col min="29" max="29" width="11.88671875" customWidth="1"/>
-    <col min="30" max="30" width="9.33203125" customWidth="1"/>
-    <col min="31" max="31" width="11.88671875" customWidth="1"/>
-    <col min="32" max="32" width="9.33203125" customWidth="1"/>
-    <col min="33" max="33" width="12.33203125" customWidth="1"/>
-    <col min="34" max="34" width="11.44140625" customWidth="1"/>
-    <col min="35" max="35" width="8.88671875" customWidth="1"/>
-    <col min="36" max="36" width="11.44140625" customWidth="1"/>
-    <col min="37" max="37" width="8.88671875" customWidth="1"/>
-    <col min="38" max="38" width="11.44140625" customWidth="1"/>
-    <col min="39" max="39" width="8.88671875" customWidth="1"/>
-    <col min="40" max="40" width="12.33203125" customWidth="1"/>
-    <col min="41" max="41" width="11.44140625" customWidth="1"/>
-    <col min="42" max="42" width="8.88671875" customWidth="1"/>
-    <col min="43" max="43" width="11.44140625" customWidth="1"/>
-    <col min="44" max="44" width="8.88671875" customWidth="1"/>
-    <col min="45" max="45" width="11.44140625" customWidth="1"/>
-    <col min="46" max="46" width="8.88671875" customWidth="1"/>
-    <col min="47" max="47" width="12.5546875" customWidth="1"/>
-    <col min="48" max="48" width="11.6640625" customWidth="1"/>
-    <col min="50" max="50" width="11.6640625" customWidth="1"/>
-    <col min="52" max="52" width="11.6640625" customWidth="1"/>
-    <col min="54" max="54" width="12.109375" customWidth="1"/>
-    <col min="55" max="55" width="11.33203125" customWidth="1"/>
-    <col min="56" max="56" width="8.6640625" customWidth="1"/>
-    <col min="57" max="57" width="11.33203125" customWidth="1"/>
-    <col min="58" max="58" width="8.6640625" customWidth="1"/>
-    <col min="59" max="59" width="11.33203125" customWidth="1"/>
-    <col min="60" max="60" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.85546875" customWidth="1"/>
+    <col min="14" max="14" width="9.28515625" customWidth="1"/>
+    <col min="15" max="15" width="11.85546875" customWidth="1"/>
+    <col min="16" max="16" width="9.28515625" customWidth="1"/>
+    <col min="17" max="17" width="11.85546875" customWidth="1"/>
+    <col min="18" max="18" width="9.28515625" customWidth="1"/>
+    <col min="19" max="19" width="13.140625" customWidth="1"/>
+    <col min="20" max="20" width="12.140625" customWidth="1"/>
+    <col min="21" max="21" width="9.5703125" customWidth="1"/>
+    <col min="22" max="22" width="12.140625" customWidth="1"/>
+    <col min="23" max="23" width="9.5703125" customWidth="1"/>
+    <col min="24" max="24" width="12.140625" customWidth="1"/>
+    <col min="25" max="25" width="9.5703125" customWidth="1"/>
+    <col min="26" max="26" width="12.7109375" customWidth="1"/>
+    <col min="27" max="27" width="11.85546875" customWidth="1"/>
+    <col min="28" max="28" width="9.28515625" customWidth="1"/>
+    <col min="29" max="29" width="11.85546875" customWidth="1"/>
+    <col min="30" max="30" width="9.28515625" customWidth="1"/>
+    <col min="31" max="31" width="11.85546875" customWidth="1"/>
+    <col min="32" max="32" width="9.28515625" customWidth="1"/>
+    <col min="33" max="33" width="12.28515625" customWidth="1"/>
+    <col min="34" max="34" width="11.42578125" customWidth="1"/>
+    <col min="35" max="35" width="8.85546875" customWidth="1"/>
+    <col min="36" max="36" width="11.42578125" customWidth="1"/>
+    <col min="37" max="37" width="8.85546875" customWidth="1"/>
+    <col min="38" max="38" width="11.42578125" customWidth="1"/>
+    <col min="39" max="39" width="8.85546875" customWidth="1"/>
+    <col min="40" max="40" width="12.28515625" customWidth="1"/>
+    <col min="41" max="41" width="11.42578125" customWidth="1"/>
+    <col min="42" max="42" width="8.85546875" customWidth="1"/>
+    <col min="43" max="43" width="11.42578125" customWidth="1"/>
+    <col min="44" max="44" width="8.85546875" customWidth="1"/>
+    <col min="45" max="45" width="11.42578125" customWidth="1"/>
+    <col min="46" max="46" width="8.85546875" customWidth="1"/>
+    <col min="47" max="47" width="12.5703125" customWidth="1"/>
+    <col min="48" max="48" width="11.7109375" customWidth="1"/>
+    <col min="50" max="50" width="11.7109375" customWidth="1"/>
+    <col min="52" max="52" width="11.7109375" customWidth="1"/>
+    <col min="54" max="54" width="12.140625" customWidth="1"/>
+    <col min="55" max="55" width="11.28515625" customWidth="1"/>
+    <col min="56" max="56" width="8.7109375" customWidth="1"/>
+    <col min="57" max="57" width="11.28515625" customWidth="1"/>
+    <col min="58" max="58" width="8.7109375" customWidth="1"/>
+    <col min="59" max="59" width="11.28515625" customWidth="1"/>
+    <col min="60" max="60" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>5</v>
       </c>
@@ -33704,7 +33717,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
         <v>45017</v>
       </c>
@@ -33886,7 +33899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>45047</v>
       </c>
@@ -34068,7 +34081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <v>45078</v>
       </c>
@@ -34250,7 +34263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <v>45108</v>
       </c>
@@ -34432,7 +34445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>45139</v>
       </c>
@@ -34614,7 +34627,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="7" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>45170</v>
       </c>
@@ -34796,7 +34809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>45200</v>
       </c>
@@ -34978,7 +34991,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="9" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>45231</v>
       </c>
@@ -35156,7 +35169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>45261</v>
       </c>
@@ -35338,7 +35351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>45292</v>
       </c>
@@ -35520,7 +35533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>45323</v>
       </c>
@@ -35702,7 +35715,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>45352</v>
       </c>
@@ -35884,7 +35897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>45383</v>
       </c>
@@ -36066,7 +36079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>45413</v>
       </c>
@@ -36248,7 +36261,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>45444</v>
       </c>
@@ -36430,7 +36443,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="17" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>45474</v>
       </c>
@@ -36612,7 +36625,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="18" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>45505</v>
       </c>
@@ -36794,7 +36807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>45536</v>
       </c>
@@ -36976,7 +36989,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="20" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>45566</v>
       </c>
@@ -37158,7 +37171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>45597</v>
       </c>
@@ -37340,7 +37353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>45627</v>
       </c>
@@ -37522,7 +37535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>45658</v>
       </c>
@@ -37704,7 +37717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>45689</v>
       </c>
@@ -37886,7 +37899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>45717</v>
       </c>
@@ -38068,7 +38081,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="26" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>45748</v>
       </c>
@@ -38250,7 +38263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>45778</v>
       </c>
@@ -38432,7 +38445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>45809</v>
       </c>
@@ -38614,7 +38627,7 @@
         <v>2.77</v>
       </c>
     </row>
-    <row r="29" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>45839</v>
       </c>
@@ -38796,7 +38809,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="30" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>45870</v>
       </c>
@@ -38978,7 +38991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>45901</v>
       </c>
@@ -39160,7 +39173,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="32" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>45931</v>
       </c>
@@ -39342,7 +39355,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="33" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>45962</v>
       </c>
@@ -39524,7 +39537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>45992</v>
       </c>
@@ -39706,7 +39719,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="35" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>46023</v>
       </c>
@@ -39888,7 +39901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>46054</v>
       </c>
@@ -40000,6 +40013,12 @@
       <c r="AK36">
         <v>0.16</v>
       </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>0</v>
+      </c>
       <c r="AN36" s="3">
         <v>46064</v>
       </c>
@@ -40064,7 +40083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>46082</v>
       </c>
@@ -40246,7 +40265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>46113</v>
       </c>
@@ -40428,7 +40447,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="39" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>46143</v>
       </c>
@@ -40610,7 +40629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>46174</v>
       </c>
@@ -40801,9 +40820,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:BH41"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:60" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:60" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>5</v>
       </c>
@@ -40921,7 +40940,7 @@
       <c r="BG1" s="10"/>
       <c r="BH1" s="10"/>
     </row>
-    <row r="2" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
         <v>45017</v>
       </c>
@@ -41007,7 +41026,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="3" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>45047</v>
       </c>
@@ -41093,7 +41112,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="4" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <v>45078</v>
       </c>
@@ -41179,7 +41198,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="5" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <v>45108</v>
       </c>
@@ -41265,7 +41284,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="6" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>45139</v>
       </c>
@@ -41351,7 +41370,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="7" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>45170</v>
       </c>
@@ -41437,7 +41456,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="8" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>45200</v>
       </c>
@@ -41523,7 +41542,7 @@
         <v>2.09</v>
       </c>
     </row>
-    <row r="9" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>45231</v>
       </c>
@@ -41609,7 +41628,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="10" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>45261</v>
       </c>
@@ -41695,7 +41714,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="11" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>45292</v>
       </c>
@@ -41781,7 +41800,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="12" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>45323</v>
       </c>
@@ -41867,7 +41886,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="13" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>45352</v>
       </c>
@@ -41953,7 +41972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>45383</v>
       </c>
@@ -42039,7 +42058,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="15" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>45413</v>
       </c>
@@ -42125,7 +42144,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="16" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>45444</v>
       </c>
@@ -42211,7 +42230,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>45474</v>
       </c>
@@ -42297,7 +42316,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>45505</v>
       </c>
@@ -42383,7 +42402,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>45536</v>
       </c>
@@ -42469,7 +42488,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>45566</v>
       </c>
@@ -42555,7 +42574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>45597</v>
       </c>
@@ -42641,7 +42660,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>45627</v>
       </c>
@@ -42727,7 +42746,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>45658</v>
       </c>
@@ -42813,7 +42832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>45689</v>
       </c>
@@ -42899,7 +42918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>45717</v>
       </c>
@@ -42985,7 +43004,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>45748</v>
       </c>
@@ -43071,7 +43090,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>45778</v>
       </c>
@@ -43157,7 +43176,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>45809</v>
       </c>
@@ -43243,7 +43262,7 @@
         <v>23.26</v>
       </c>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>45839</v>
       </c>
@@ -43329,7 +43348,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>45870</v>
       </c>
@@ -43415,7 +43434,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>45901</v>
       </c>
@@ -43501,7 +43520,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>45901</v>
       </c>
@@ -43587,7 +43606,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>45931</v>
       </c>
@@ -43673,7 +43692,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>45962</v>
       </c>
@@ -43759,7 +43778,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>45992</v>
       </c>
@@ -43845,7 +43864,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>46023</v>
       </c>
@@ -43931,7 +43950,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>46054</v>
       </c>
@@ -44017,7 +44036,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>46082</v>
       </c>
@@ -44103,7 +44122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>46113</v>
       </c>
@@ -44189,7 +44208,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>46143</v>
       </c>
@@ -44275,7 +44294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>46174</v>
       </c>
@@ -44370,12 +44389,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:CN98"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:46" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>5</v>
       </c>
@@ -44515,7 +44534,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="2" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>38384</v>
       </c>
@@ -44637,7 +44656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>38412</v>
       </c>
@@ -44759,7 +44778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>38443</v>
       </c>
@@ -44881,7 +44900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>38473</v>
       </c>
@@ -45003,7 +45022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>38504</v>
       </c>
@@ -45125,7 +45144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>38534</v>
       </c>
@@ -45247,7 +45266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>38565</v>
       </c>
@@ -45369,7 +45388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>38596</v>
       </c>
@@ -45491,7 +45510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>38657</v>
       </c>
@@ -45613,7 +45632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>38687</v>
       </c>
@@ -45735,7 +45754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>38718</v>
       </c>
@@ -45857,7 +45876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>38749</v>
       </c>
@@ -45979,7 +45998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>38777</v>
       </c>
@@ -46101,7 +46120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>38808</v>
       </c>
@@ -46223,7 +46242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>38838</v>
       </c>
@@ -46345,7 +46364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>38869</v>
       </c>
@@ -46467,7 +46486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>38899</v>
       </c>
@@ -46589,7 +46608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>38930</v>
       </c>
@@ -46711,7 +46730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>38961</v>
       </c>
@@ -46833,7 +46852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>38991</v>
       </c>
@@ -46955,7 +46974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>39022</v>
       </c>
@@ -47077,7 +47096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>39052</v>
       </c>
@@ -47199,7 +47218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>39083</v>
       </c>
@@ -47321,7 +47340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>39114</v>
       </c>
@@ -47443,7 +47462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>39142</v>
       </c>
@@ -47565,7 +47584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>39173</v>
       </c>
@@ -47687,7 +47706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>39203</v>
       </c>
@@ -47809,7 +47828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>39234</v>
       </c>
@@ -47931,7 +47950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>39264</v>
       </c>
@@ -48053,7 +48072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>39295</v>
       </c>
@@ -48175,7 +48194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>39326</v>
       </c>
@@ -48297,7 +48316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>39356</v>
       </c>
@@ -48419,7 +48438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>39387</v>
       </c>
@@ -48541,7 +48560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>39417</v>
       </c>
@@ -48663,7 +48682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>39448</v>
       </c>
@@ -48785,7 +48804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>39479</v>
       </c>
@@ -48907,7 +48926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>39508</v>
       </c>
@@ -49029,7 +49048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>39539</v>
       </c>
@@ -49151,7 +49170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>39569</v>
       </c>
@@ -49273,7 +49292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>39600</v>
       </c>
@@ -49395,7 +49414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>39630</v>
       </c>
@@ -49517,7 +49536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>39661</v>
       </c>
@@ -49639,7 +49658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>39692</v>
       </c>
@@ -49761,7 +49780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>39722</v>
       </c>
@@ -49883,7 +49902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>39753</v>
       </c>
@@ -50005,7 +50024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>39783</v>
       </c>
@@ -50127,7 +50146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>39814</v>
       </c>
@@ -50249,7 +50268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>39845</v>
       </c>
@@ -50371,7 +50390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>39873</v>
       </c>
@@ -50493,7 +50512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>39904</v>
       </c>
@@ -50615,7 +50634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>39934</v>
       </c>
@@ -50737,7 +50756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>39965</v>
       </c>
@@ -50859,7 +50878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>39995</v>
       </c>
@@ -50981,7 +51000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>40026</v>
       </c>
@@ -51103,7 +51122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>40057</v>
       </c>
@@ -51225,7 +51244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>40087</v>
       </c>
@@ -51347,7 +51366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>40118</v>
       </c>
@@ -51469,7 +51488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>40148</v>
       </c>
@@ -51591,7 +51610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A60" s="11">
         <v>45017</v>
       </c>
@@ -51739,7 +51758,7 @@
       <c r="BA60" s="3"/>
       <c r="BC60" s="3"/>
     </row>
-    <row r="61" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A61" s="11">
         <v>45047</v>
       </c>
@@ -51888,7 +51907,7 @@
       <c r="BB61" s="3"/>
       <c r="BC61" s="3"/>
     </row>
-    <row r="62" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A62" s="11">
         <v>45078</v>
       </c>
@@ -52037,7 +52056,7 @@
       <c r="BB62" s="3"/>
       <c r="BC62" s="3"/>
     </row>
-    <row r="63" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A63" s="11">
         <v>45108</v>
       </c>
@@ -52186,7 +52205,7 @@
       <c r="BB63" s="3"/>
       <c r="BC63" s="3"/>
     </row>
-    <row r="64" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A64" s="11">
         <v>45139</v>
       </c>
@@ -52335,7 +52354,7 @@
       <c r="BB64" s="3"/>
       <c r="BC64" s="3"/>
     </row>
-    <row r="65" spans="1:92" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:92" x14ac:dyDescent="0.25">
       <c r="A65" s="11">
         <v>45170</v>
       </c>
@@ -52484,7 +52503,7 @@
       <c r="BB65" s="3"/>
       <c r="BC65" s="3"/>
     </row>
-    <row r="66" spans="1:92" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:92" x14ac:dyDescent="0.25">
       <c r="A66" s="11">
         <v>45200</v>
       </c>
@@ -52633,7 +52652,7 @@
       <c r="BB66" s="3"/>
       <c r="BC66" s="3"/>
     </row>
-    <row r="67" spans="1:92" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:92" x14ac:dyDescent="0.25">
       <c r="A67" s="11">
         <v>45231</v>
       </c>
@@ -52782,7 +52801,7 @@
       <c r="BB67" s="3"/>
       <c r="BC67" s="3"/>
     </row>
-    <row r="68" spans="1:92" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:92" x14ac:dyDescent="0.25">
       <c r="A68" s="11">
         <v>45261</v>
       </c>
@@ -52931,7 +52950,7 @@
       <c r="BB68" s="3"/>
       <c r="BC68" s="3"/>
     </row>
-    <row r="69" spans="1:92" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:92" x14ac:dyDescent="0.25">
       <c r="A69" s="11">
         <v>45292</v>
       </c>
@@ -53080,7 +53099,7 @@
       <c r="BB69" s="3"/>
       <c r="BC69" s="3"/>
     </row>
-    <row r="70" spans="1:92" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:92" x14ac:dyDescent="0.25">
       <c r="A70" s="11">
         <v>45323</v>
       </c>
@@ -53229,7 +53248,7 @@
       <c r="BB70" s="3"/>
       <c r="BC70" s="3"/>
     </row>
-    <row r="71" spans="1:92" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:92" x14ac:dyDescent="0.25">
       <c r="A71" s="11">
         <v>45352</v>
       </c>
@@ -53378,7 +53397,7 @@
       <c r="BB71" s="3"/>
       <c r="BC71" s="3"/>
     </row>
-    <row r="72" spans="1:92" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:92" x14ac:dyDescent="0.25">
       <c r="A72" s="11">
         <v>45383</v>
       </c>
@@ -53556,7 +53575,7 @@
       <c r="CM72" s="13"/>
       <c r="CN72" s="13"/>
     </row>
-    <row r="73" spans="1:92" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:92" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>45413</v>
       </c>
@@ -53705,7 +53724,7 @@
       <c r="BB73" s="3"/>
       <c r="BC73" s="3"/>
     </row>
-    <row r="74" spans="1:92" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:92" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>45444</v>
       </c>
@@ -53854,7 +53873,7 @@
       <c r="BB74" s="3"/>
       <c r="BC74" s="3"/>
     </row>
-    <row r="75" spans="1:92" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:92" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>45474</v>
       </c>
@@ -53994,7 +54013,7 @@
         <v>13.33</v>
       </c>
     </row>
-    <row r="76" spans="1:92" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:92" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>45505</v>
       </c>
@@ -54134,7 +54153,7 @@
         <v>7.69</v>
       </c>
     </row>
-    <row r="77" spans="1:92" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:92" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>45536</v>
       </c>
@@ -54274,7 +54293,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="78" spans="1:92" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:92" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>45566</v>
       </c>
@@ -54414,7 +54433,7 @@
         <v>28.57</v>
       </c>
     </row>
-    <row r="79" spans="1:92" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:92" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>45597</v>
       </c>
@@ -54554,7 +54573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:92" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:92" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>45627</v>
       </c>
@@ -54694,7 +54713,7 @@
         <v>7.14</v>
       </c>
     </row>
-    <row r="81" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <v>45658</v>
       </c>
@@ -54834,7 +54853,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="82" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <v>45689</v>
       </c>
@@ -54974,7 +54993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <v>45717</v>
       </c>
@@ -55114,7 +55133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <v>45748</v>
       </c>
@@ -55254,7 +55273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <v>45778</v>
       </c>
@@ -55394,7 +55413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <v>45809</v>
       </c>
@@ -55534,7 +55553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>45839</v>
       </c>
@@ -55674,7 +55693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>45870</v>
       </c>
@@ -55814,7 +55833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>45901</v>
       </c>
@@ -55954,7 +55973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>45931</v>
       </c>
@@ -56094,7 +56113,7 @@
         <v>53.85</v>
       </c>
     </row>
-    <row r="91" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>45962</v>
       </c>
@@ -56234,7 +56253,7 @@
         <v>35.71</v>
       </c>
     </row>
-    <row r="92" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>45992</v>
       </c>
@@ -56374,7 +56393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <v>46023</v>
       </c>
@@ -56514,7 +56533,7 @@
         <v>7.69</v>
       </c>
     </row>
-    <row r="94" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <v>46054</v>
       </c>
@@ -56654,7 +56673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
         <v>46082</v>
       </c>
@@ -56794,7 +56813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
         <v>46113</v>
       </c>
@@ -56934,7 +56953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
         <v>46143</v>
       </c>
@@ -57074,7 +57093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
         <v>46174</v>
       </c>
@@ -57223,50 +57242,50 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:AM33"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" customWidth="1"/>
-    <col min="4" max="4" width="13.33203125" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="19.33203125" customWidth="1"/>
-    <col min="7" max="7" width="17.5546875" customWidth="1"/>
-    <col min="8" max="8" width="14.88671875" customWidth="1"/>
-    <col min="9" max="9" width="15.88671875" customWidth="1"/>
-    <col min="10" max="10" width="13.33203125" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" customWidth="1"/>
     <col min="11" max="11" width="22" customWidth="1"/>
-    <col min="12" max="12" width="19.33203125" customWidth="1"/>
-    <col min="13" max="13" width="17.5546875" customWidth="1"/>
-    <col min="14" max="14" width="14.88671875" customWidth="1"/>
-    <col min="15" max="15" width="15.88671875" customWidth="1"/>
-    <col min="16" max="16" width="13.33203125" customWidth="1"/>
+    <col min="12" max="12" width="19.28515625" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" customWidth="1"/>
+    <col min="15" max="15" width="15.85546875" customWidth="1"/>
+    <col min="16" max="16" width="13.28515625" customWidth="1"/>
     <col min="17" max="17" width="22" customWidth="1"/>
-    <col min="18" max="18" width="19.33203125" customWidth="1"/>
-    <col min="19" max="19" width="17.5546875" customWidth="1"/>
-    <col min="20" max="20" width="14.88671875" customWidth="1"/>
-    <col min="21" max="21" width="13.109375" customWidth="1"/>
-    <col min="22" max="22" width="16.109375" customWidth="1"/>
-    <col min="23" max="23" width="13.5546875" customWidth="1"/>
-    <col min="24" max="24" width="22.33203125" customWidth="1"/>
-    <col min="25" max="25" width="19.5546875" customWidth="1"/>
-    <col min="26" max="26" width="17.88671875" customWidth="1"/>
-    <col min="27" max="27" width="15.109375" customWidth="1"/>
-    <col min="28" max="28" width="16.109375" customWidth="1"/>
-    <col min="29" max="29" width="13.5546875" customWidth="1"/>
-    <col min="30" max="30" width="22.33203125" customWidth="1"/>
-    <col min="31" max="31" width="19.5546875" customWidth="1"/>
-    <col min="32" max="32" width="17.88671875" customWidth="1"/>
-    <col min="33" max="33" width="15.109375" customWidth="1"/>
-    <col min="34" max="34" width="16.109375" customWidth="1"/>
-    <col min="35" max="35" width="13.5546875" customWidth="1"/>
-    <col min="36" max="36" width="22.33203125" customWidth="1"/>
-    <col min="37" max="37" width="19.5546875" customWidth="1"/>
-    <col min="38" max="38" width="17.88671875" customWidth="1"/>
-    <col min="39" max="39" width="15.109375" customWidth="1"/>
+    <col min="18" max="18" width="19.28515625" customWidth="1"/>
+    <col min="19" max="19" width="17.5703125" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" customWidth="1"/>
+    <col min="21" max="21" width="13.140625" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" customWidth="1"/>
+    <col min="23" max="23" width="13.5703125" customWidth="1"/>
+    <col min="24" max="24" width="22.28515625" customWidth="1"/>
+    <col min="25" max="25" width="19.5703125" customWidth="1"/>
+    <col min="26" max="26" width="17.85546875" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" customWidth="1"/>
+    <col min="28" max="28" width="16.140625" customWidth="1"/>
+    <col min="29" max="29" width="13.5703125" customWidth="1"/>
+    <col min="30" max="30" width="22.28515625" customWidth="1"/>
+    <col min="31" max="31" width="19.5703125" customWidth="1"/>
+    <col min="32" max="32" width="17.85546875" customWidth="1"/>
+    <col min="33" max="33" width="15.140625" customWidth="1"/>
+    <col min="34" max="34" width="16.140625" customWidth="1"/>
+    <col min="35" max="35" width="13.5703125" customWidth="1"/>
+    <col min="36" max="36" width="22.28515625" customWidth="1"/>
+    <col min="37" max="37" width="19.5703125" customWidth="1"/>
+    <col min="38" max="38" width="17.85546875" customWidth="1"/>
+    <col min="39" max="39" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -57385,7 +57404,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>45231</v>
       </c>
@@ -57486,7 +57505,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>45261</v>
       </c>
@@ -57605,7 +57624,7 @@
         <v>2.67</v>
       </c>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>45292</v>
       </c>
@@ -57688,7 +57707,7 @@
         <v>1.86</v>
       </c>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>45323</v>
       </c>
@@ -57807,7 +57826,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>45352</v>
       </c>
@@ -57926,7 +57945,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>45383</v>
       </c>
@@ -58009,7 +58028,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>45413</v>
       </c>
@@ -58128,7 +58147,7 @@
         <v>5.51</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>45444</v>
       </c>
@@ -58247,7 +58266,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>45474</v>
       </c>
@@ -58366,7 +58385,7 @@
         <v>2.04</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>45505</v>
       </c>
@@ -58467,7 +58486,7 @@
         <v>2.91</v>
       </c>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>45536</v>
       </c>
@@ -58568,7 +58587,7 @@
         <v>3.17</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>45566</v>
       </c>
@@ -58687,7 +58706,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>45597</v>
       </c>
@@ -58806,7 +58825,7 @@
         <v>2.59</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>45627</v>
       </c>
@@ -58898,7 +58917,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>45658</v>
       </c>
@@ -59017,7 +59036,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="17" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>45689</v>
       </c>
@@ -59064,7 +59083,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="18" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>45717</v>
       </c>
@@ -59174,7 +59193,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="19" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>45748</v>
       </c>
@@ -59293,7 +59312,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>45778</v>
       </c>
@@ -59400,7 +59419,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>45809</v>
       </c>
@@ -59519,7 +59538,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="22" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>45839</v>
       </c>
@@ -59638,7 +59657,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="23" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>45870</v>
       </c>
@@ -59757,7 +59776,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="24" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>45901</v>
       </c>
@@ -59876,7 +59895,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="25" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>45931</v>
       </c>
@@ -59995,7 +60014,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="26" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>45962</v>
       </c>
@@ -60114,7 +60133,7 @@
         <v>1.95</v>
       </c>
     </row>
-    <row r="27" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>45992</v>
       </c>
@@ -60233,7 +60252,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="28" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>46023</v>
       </c>
@@ -60352,7 +60371,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="29" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>46054</v>
       </c>
@@ -60471,7 +60490,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>46082</v>
       </c>
@@ -60581,7 +60600,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="31" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>46113</v>
       </c>
@@ -60700,7 +60719,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="32" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>46143</v>
       </c>
@@ -60819,7 +60838,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>46174</v>
       </c>
@@ -60947,9 +60966,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:N33"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -60993,7 +61012,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>45231</v>
       </c>
@@ -61037,7 +61056,7 @@
         <v>3.44</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>45261</v>
       </c>
@@ -61081,7 +61100,7 @@
         <v>4.3899999999999997</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>45292</v>
       </c>
@@ -61125,7 +61144,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>45323</v>
       </c>
@@ -61169,7 +61188,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>45352</v>
       </c>
@@ -61213,7 +61232,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>45383</v>
       </c>
@@ -61257,7 +61276,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>45413</v>
       </c>
@@ -61301,7 +61320,7 @@
         <v>4.6399999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>45444</v>
       </c>
@@ -61345,7 +61364,7 @@
         <v>2.2400000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>45474</v>
       </c>
@@ -61389,7 +61408,7 @@
         <v>2.87</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>45505</v>
       </c>
@@ -61433,7 +61452,7 @@
         <v>2.63</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>45536</v>
       </c>
@@ -61477,7 +61496,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>45566</v>
       </c>
@@ -61521,7 +61540,7 @@
         <v>3.23</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>45597</v>
       </c>
@@ -61565,7 +61584,7 @@
         <v>2.17</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>45627</v>
       </c>
@@ -61609,7 +61628,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>45658</v>
       </c>
@@ -61653,7 +61672,7 @@
         <v>1.51</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>45689</v>
       </c>
@@ -61673,7 +61692,7 @@
         <v>4.93</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>45717</v>
       </c>
@@ -61717,7 +61736,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>45748</v>
       </c>
@@ -61761,7 +61780,7 @@
         <v>1.57</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>45778</v>
       </c>
@@ -61805,7 +61824,7 @@
         <v>1.95</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>45809</v>
       </c>
@@ -61849,7 +61868,7 @@
         <v>2.02</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>45839</v>
       </c>
@@ -61893,7 +61912,7 @@
         <v>1.59</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>45870</v>
       </c>
@@ -61937,7 +61956,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>45901</v>
       </c>
@@ -61981,7 +62000,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>45931</v>
       </c>
@@ -62025,7 +62044,7 @@
         <v>5.57</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>45962</v>
       </c>
@@ -62069,7 +62088,7 @@
         <v>3.32</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>45992</v>
       </c>
@@ -62113,7 +62132,7 @@
         <v>4.29</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>46023</v>
       </c>
@@ -62157,7 +62176,7 @@
         <v>1.65</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>46054</v>
       </c>
@@ -62201,7 +62220,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>46082</v>
       </c>
@@ -62245,7 +62264,7 @@
         <v>3.15</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>46113</v>
       </c>
@@ -62289,7 +62308,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>46143</v>
       </c>
@@ -62333,7 +62352,7 @@
         <v>2.12</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>46174</v>
       </c>
